--- a/data/trans_orig/P19F$mañana-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016</t>
+          <t>Población según el momento del día en que acostumbra a cepillarse los dientes (multirrespuesta) en 2016 (tasa de respuesta: 93,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133235</t>
+          <t>135849</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>171455</t>
+          <t>173505</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,27%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>131374</t>
+          <t>130152</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168095</t>
+          <t>168165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>274324</t>
+          <t>273143</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>329221</t>
+          <t>326623</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97703</t>
+          <t>98390</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133932</t>
+          <t>133432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92153</t>
+          <t>91883</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126665</t>
+          <t>126160</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>199233</t>
+          <t>196192</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246793</t>
+          <t>247024</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,43%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273605</t>
+          <t>273020</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>303923</t>
+          <t>305324</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>320170</t>
+          <t>319944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>344705</t>
+          <t>344538</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>604755</t>
+          <t>603226</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>642538</t>
+          <t>642614</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,97%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>192748</t>
+          <t>193516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241730</t>
+          <t>240102</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,92%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220197</t>
+          <t>220323</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>266225</t>
+          <t>267921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>423903</t>
+          <t>427710</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>493259</t>
+          <t>497334</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160774</t>
+          <t>161085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206303</t>
+          <t>206249</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164710</t>
+          <t>163827</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208528</t>
+          <t>208966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333032</t>
+          <t>333843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401789</t>
+          <t>398938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>419875</t>
+          <t>420873</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>459858</t>
+          <t>460984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>418989</t>
+          <t>419138</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>456928</t>
+          <t>455673</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>852571</t>
+          <t>852567</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>906453</t>
+          <t>905002</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118314</t>
+          <t>118877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>156444</t>
+          <t>157234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134834</t>
+          <t>133379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>171947</t>
+          <t>172885</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>263849</t>
+          <t>260037</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316051</t>
+          <t>316568</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>118852</t>
+          <t>117258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156214</t>
+          <t>159072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117926</t>
+          <t>118851</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155773</t>
+          <t>156292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246870</t>
+          <t>246877</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301917</t>
+          <t>302562</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>248604</t>
+          <t>250372</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>287484</t>
+          <t>289976</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>238912</t>
+          <t>238904</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>275095</t>
+          <t>275910</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>498889</t>
+          <t>495185</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>552372</t>
+          <t>552088</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,19%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198960</t>
+          <t>198871</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>242270</t>
+          <t>240915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218137</t>
+          <t>217645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260825</t>
+          <t>261317</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>431646</t>
+          <t>430724</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>492037</t>
+          <t>490509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,98%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98285</t>
+          <t>97233</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134408</t>
+          <t>134695</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107736</t>
+          <t>107174</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148000</t>
+          <t>148068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216718</t>
+          <t>214473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>269998</t>
+          <t>267619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,0%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>364941</t>
+          <t>365587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>395148</t>
+          <t>395365</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>359278</t>
+          <t>358475</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>390664</t>
+          <t>390565</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>734289</t>
+          <t>734163</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>778262</t>
+          <t>779731</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>687665</t>
+          <t>678823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>768305</t>
+          <t>766106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>740774</t>
+          <t>740350</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>825126</t>
+          <t>828265</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,35%</t>
+          <t>47,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1455044</t>
+          <t>1450680</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1575069</t>
+          <t>1567574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,52%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>511174</t>
+          <t>508029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>586444</t>
+          <t>588603</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>519259</t>
+          <t>522131</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>596831</t>
+          <t>603307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1042418</t>
+          <t>1046212</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1157740</t>
+          <t>1160166</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1344079</t>
+          <t>1346408</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1415670</t>
+          <t>1417911</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,56%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1374368</t>
+          <t>1369135</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1438597</t>
+          <t>1436644</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,45%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2738106</t>
+          <t>2737006</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2840362</t>
+          <t>2840885</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>135849</t>
+          <t>135465</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>173505</t>
+          <t>171079</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>130152</t>
+          <t>129969</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>168165</t>
+          <t>169831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>273143</t>
+          <t>275100</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>326623</t>
+          <t>328174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,42%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>98390</t>
+          <t>97434</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133432</t>
+          <t>131772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91883</t>
+          <t>92421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126160</t>
+          <t>126861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>196192</t>
+          <t>200424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247024</t>
+          <t>250644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>273020</t>
+          <t>274161</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305324</t>
+          <t>304738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>319944</t>
+          <t>320168</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>344538</t>
+          <t>344867</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>603226</t>
+          <t>605360</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>642614</t>
+          <t>645031</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>193516</t>
+          <t>192499</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>240102</t>
+          <t>240354</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>220323</t>
+          <t>221733</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>267921</t>
+          <t>264893</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>427710</t>
+          <t>424903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>497334</t>
+          <t>494470</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,8%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>161085</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206249</t>
+          <t>202458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>163827</t>
+          <t>164662</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>208966</t>
+          <t>210465</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333843</t>
+          <t>335781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398938</t>
+          <t>401283</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>420873</t>
+          <t>419687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>460984</t>
+          <t>461530</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>419138</t>
+          <t>418093</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>455673</t>
+          <t>456480</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>852567</t>
+          <t>852775</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>905002</t>
+          <t>907022</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118877</t>
+          <t>118996</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157234</t>
+          <t>159280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>133379</t>
+          <t>132099</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172885</t>
+          <t>170542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260037</t>
+          <t>260016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316568</t>
+          <t>316118</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117258</t>
+          <t>117043</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159072</t>
+          <t>156543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118851</t>
+          <t>119008</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>156292</t>
+          <t>155326</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246877</t>
+          <t>244592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302562</t>
+          <t>302697</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>250372</t>
+          <t>249012</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>289976</t>
+          <t>288553</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>238904</t>
+          <t>239695</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>275910</t>
+          <t>275679</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495185</t>
+          <t>497157</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>552088</t>
+          <t>551957</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>198871</t>
+          <t>199445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>240915</t>
+          <t>241942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,53%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>217645</t>
+          <t>215982</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>261317</t>
+          <t>262265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>430724</t>
+          <t>428716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>490509</t>
+          <t>490327</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,96%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97233</t>
+          <t>97327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134695</t>
+          <t>133754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107174</t>
+          <t>108716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148068</t>
+          <t>149627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>214473</t>
+          <t>215844</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>267619</t>
+          <t>272242</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -1985,12 +1985,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>365587</t>
+          <t>365670</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>395365</t>
+          <t>395958</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,12 +2000,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>358475</t>
+          <t>358674</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>390565</t>
+          <t>392269</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2055,12 +2055,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>734163</t>
+          <t>733925</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>779731</t>
+          <t>777886</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>678823</t>
+          <t>688651</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>766106</t>
+          <t>772357</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>740350</t>
+          <t>741817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>828265</t>
+          <t>827572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1450680</t>
+          <t>1450668</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1567574</t>
+          <t>1565117</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,52%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>508029</t>
+          <t>505745</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>588603</t>
+          <t>589137</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522131</t>
+          <t>519547</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>603307</t>
+          <t>596318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1046212</t>
+          <t>1054609</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1160166</t>
+          <t>1162218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1346408</t>
+          <t>1345093</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1417911</t>
+          <t>1415764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,12 +2343,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1369135</t>
+          <t>1370750</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1436644</t>
+          <t>1440189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,12 +2378,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,12 +2398,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2737006</t>
+          <t>2738440</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2840885</t>
+          <t>2840308</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19F$mañana-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19F$mañana-Habitat-trans_orig.xlsx
@@ -828,112 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>284</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>114554</t>
+          <t>290961</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97434</t>
+          <t>274161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>131772</t>
+          <t>304738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>111</t>
+          <t>334</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>108564</t>
+          <t>333537</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92421</t>
+          <t>320168</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126861</t>
+          <t>344867</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>618</t>
         </is>
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>223118</t>
+          <t>624497</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>200424</t>
+          <t>605360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>250644</t>
+          <t>645031</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>87,3%</t>
         </is>
       </c>
     </row>
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>112</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>290961</t>
+          <t>114554</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>274161</t>
+          <t>97434</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>304738</t>
+          <t>131772</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>111</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>333537</t>
+          <t>108564</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>320168</t>
+          <t>92421</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>344867</t>
+          <t>126861</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>223</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>624497</t>
+          <t>223118</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>605360</t>
+          <t>200424</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>645031</t>
+          <t>250644</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>33,92%</t>
         </is>
       </c>
     </row>
@@ -1171,112 +1171,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>415</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>181956</t>
+          <t>441387</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158237</t>
+          <t>419687</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202458</t>
+          <t>461530</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>412</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>186441</t>
+          <t>439387</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164662</t>
+          <t>418093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>210465</t>
+          <t>456480</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>827</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>368397</t>
+          <t>880774</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>335781</t>
+          <t>852775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>401283</t>
+          <t>907022</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>82,17%</t>
         </is>
       </c>
     </row>
@@ -1284,112 +1284,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>415</t>
+          <t>171</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>441387</t>
+          <t>181956</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>419687</t>
+          <t>158237</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>461530</t>
+          <t>202458</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>412</t>
+          <t>177</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>439387</t>
+          <t>186441</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>418093</t>
+          <t>164662</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>456480</t>
+          <t>210465</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>348</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>880774</t>
+          <t>368397</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>852775</t>
+          <t>335781</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>907022</t>
+          <t>401283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>36,36%</t>
         </is>
       </c>
     </row>
@@ -1514,112 +1514,112 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>247</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>136475</t>
+          <t>268744</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>117043</t>
+          <t>249012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>156543</t>
+          <t>288553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>242</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>136022</t>
+          <t>257679</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119008</t>
+          <t>239695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>155326</t>
+          <t>275679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>67,15%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>71,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>489</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>272498</t>
+          <t>526423</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>244592</t>
+          <t>497157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302697</t>
+          <t>551957</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -1627,112 +1627,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>268744</t>
+          <t>136475</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>249012</t>
+          <t>117043</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>288553</t>
+          <t>156543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>257679</t>
+          <t>136022</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>239695</t>
+          <t>119008</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>275679</t>
+          <t>155326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>489</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>526423</t>
+          <t>272498</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>497157</t>
+          <t>244592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>551957</t>
+          <t>302697</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -1857,112 +1857,112 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>379</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>114599</t>
+          <t>381622</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>97327</t>
+          <t>365670</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>133754</t>
+          <t>395958</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>344</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>127534</t>
+          <t>375255</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108716</t>
+          <t>358674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149627</t>
+          <t>392269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>723</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>242133</t>
+          <t>756877</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215844</t>
+          <t>733925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272242</t>
+          <t>777886</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -1970,112 +1970,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>113</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>381622</t>
+          <t>114599</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>365670</t>
+          <t>97327</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>395958</t>
+          <t>133754</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>117</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>375255</t>
+          <t>127534</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>358674</t>
+          <t>108716</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>392269</t>
+          <t>149627</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>230</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>756877</t>
+          <t>242133</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>733925</t>
+          <t>215844</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>777886</t>
+          <t>272242</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>30,52%</t>
         </is>
       </c>
     </row>
@@ -2200,112 +2200,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Noche</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>547584</t>
+          <t>1382714</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>505745</t>
+          <t>1345093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>589137</t>
+          <t>1415764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>558561</t>
+          <t>1405857</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>519547</t>
+          <t>1370750</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>596318</t>
+          <t>1440189</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1106145</t>
+          <t>2788572</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1054609</t>
+          <t>2738440</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1162218</t>
+          <t>2840308</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -2313,112 +2313,112 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Noche</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>521</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1382714</t>
+          <t>547584</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1345093</t>
+          <t>505745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1415764</t>
+          <t>589137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>536</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1405857</t>
+          <t>558561</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1370750</t>
+          <t>519547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1440189</t>
+          <t>596318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2788572</t>
+          <t>1106145</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2738440</t>
+          <t>1054609</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2840308</t>
+          <t>1162218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>33,01%</t>
         </is>
       </c>
     </row>
